--- a/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_origin_comparison.xlsx
+++ b/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_origin_comparison.xlsx
@@ -292,12 +292,12 @@
     <t>lcc_women_share</t>
   </si>
   <si>
+    <t>any_serious_or_sensitive_case_3m</t>
+  </si>
+  <si>
     <t>any_child_or_sgbv_case_3m</t>
   </si>
   <si>
-    <t>any_serious_or_sensitive_case_3m</t>
-  </si>
-  <si>
     <t>can_record_runyankore</t>
   </si>
   <si>
@@ -523,10 +523,10 @@
     <t>Share of current LCC/LC committee members who are women</t>
   </si>
   <si>
+    <t>Any child, SGBV, or other serious/sensitive case in past 3 months</t>
+  </si>
+  <si>
     <t>LCC received child-related or SGBV case in past 3 months</t>
-  </si>
-  <si>
-    <t>Any child, SGBV, or other serious/sensitive case in past 3 months</t>
   </si>
   <si>
     <t>Can complete LCC records in Runyankore/Runyakitara</t>
@@ -5840,10 +5840,10 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D58" s="1">
         <v>107</v>
@@ -5872,10 +5872,10 @@
         <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D59" s="1">
         <v>107</v>
